--- a/out/LSTM-S4_repeat_5_000006.xlsx
+++ b/out/LSTM-S4_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6502,14 +6502,14 @@
       </c>
       <c r="IZ7" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.958776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22402,14 +22402,14 @@
       </c>
       <c r="IZ27" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002559727371013723</v>
+        <v>-5.113152705365792e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3294566415038532</v>
+        <v>0.06581025827228758</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6595371953357327</v>
+        <v>0.1317450612097988</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07608517746417377</v>
+        <v>-0.01519829364927153</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2531154913025783</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2531154913025783</v>
+        <v>0.05056083309596241</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2528466879493199</v>
+        <v>0.05049346794002224</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8258220351288877</v>
+        <v>0.2069603280649097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.90613516289671</v>
+        <v>0.4648262304554276</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.158011741345247</v>
+        <v>0.03959946472118359</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.395131484814231</v>
+        <v>0.3367629381030302</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2767723329611982</v>
+        <v>0.0693624355333953</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.790742301011319</v>
+        <v>0.4359076316691118</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1515708397016076</v>
+        <v>0.0379851555764479</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.816872650977054</v>
+        <v>0.4424561980214322</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06260096416645966</v>
+        <v>0.01568861925315071</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.790344846120656</v>
+        <v>0.4358079836439788</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07799542929861515</v>
+        <v>0.0195461828627473</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.883745247842975</v>
+        <v>0.4592153450370701</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04696273269945372</v>
+        <v>0.01176817925537965</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.899623538460786</v>
+        <v>0.463193604961955</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03570519977904496</v>
+        <v>0.008945698889074837</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.924049955879539</v>
+        <v>0.4693134159177437</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01579250278218995</v>
+        <v>0.003953926535315225</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.919898270341701</v>
+        <v>0.4682690490630101</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01253039271187114</v>
+        <v>0.003137675919314173</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.929161942552878</v>
+        <v>0.470587744349756</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006211178454313042</v>
+        <v>0.001553422204039044</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.929045999195319</v>
+        <v>0.4705549303812415</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00360822732607189</v>
+        <v>0.0008997614318907874</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.930050903165182</v>
+        <v>0.470803118930717</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001801613663035945</v>
+        <v>0.0004488353163182084</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.930043653809215</v>
+        <v>0.470797553875112</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008890155785007095</v>
+        <v>0.0002192225566657728</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.930016022702859</v>
+        <v>0.4707868779063155</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005123361805749242</v>
+        <v>0.0001251684583382067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.930154548917932</v>
+        <v>0.4708178743160781</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001690936688898088</v>
+        <v>3.740743216546624e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.929976636127028</v>
+        <v>0.4707696475226011</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>1.745791147271043e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.929972605283798</v>
+        <v>0.470764896024337</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>7.230980650542531e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.929975372216664</v>
+        <v>0.4707618871525233</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>-2.596391060734771e-07</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.929968820330935</v>
+        <v>0.4707565006683657</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>-2.090799254370459e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.92996919889918</v>
+        <v>0.4707531160499149</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.929962531935309</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.929958669860213</v>
+        <v>0.4707478291546989</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.929954122548028</v>
+        <v>0.4707480574757336</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.929954212492678</v>
+        <v>0.4707481474203835</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.929953354559093</v>
+        <v>0.4707472894867987</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.929953582880128</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.929952787215916</v>
+        <v>0.4707467221436217</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.929952849485289</v>
+        <v>0.4707467844129947</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.929952877160566</v>
+        <v>0.4707468120882716</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.929953029374589</v>
+        <v>0.4707469643022949</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.929952683433627</v>
+        <v>0.4707466183613331</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.929952759540639</v>
+        <v>0.4707466944683448</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.9299529255923</v>
+        <v>0.4707468605200064</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.9299532853709</v>
+        <v>0.4707472202986064</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.929953306127358</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.929953409909646</v>
+        <v>0.4707473448373526</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.929953638230681</v>
+        <v>0.4707475731583873</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.929953513691935</v>
+        <v>0.4707474486196411</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.929953541367212</v>
+        <v>0.470747476294918</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.929953596717766</v>
+        <v>0.470747531645472</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.929953859632897</v>
+        <v>0.4707477945606026</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.929953776607066</v>
+        <v>0.4707477115347719</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.929953569042489</v>
+        <v>0.470747503970195</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.929953582880128</v>
+        <v>0.4707475178078334</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.929953721256512</v>
+        <v>0.4707476561842181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.929953437584924</v>
+        <v>0.4707473725126295</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.929953264614443</v>
+        <v>0.4707471995421487</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.929953160832155</v>
+        <v>0.4707470957598602</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.929953306127358</v>
+        <v>0.4707472410550642</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.929953548286031</v>
+        <v>0.4707474832137374</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.929953375315551</v>
+        <v>0.4707473102432564</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.929953077806324</v>
+        <v>0.4707470127340295</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.929953063968685</v>
+        <v>0.4707469988963909</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.929952697271266</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.929952697271266</v>
+        <v>0.4707466321989717</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.929952635001893</v>
+        <v>0.4707465699295986</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.929952531219604</v>
+        <v>0.4707464661473101</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.929952358249123</v>
+        <v>0.4707462931768294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.929952406680858</v>
+        <v>0.4707463416085639</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.929952046902258</v>
+        <v>0.4707459818299639</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.929952005389343</v>
+        <v>0.4707459403170485</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.929952060739896</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.92995211609045</v>
+        <v>0.4707460510181561</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.929952157603366</v>
+        <v>0.4707460925310715</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.929951887769416</v>
+        <v>0.4707458226971214</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.929951943119969</v>
+        <v>0.4707458780476754</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.929952088415173</v>
+        <v>0.4707460233428792</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.929952053821077</v>
+        <v>0.470745988748783</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.929952039983439</v>
+        <v>0.4707459749111444</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.929952129928089</v>
+        <v>0.4707460648557947</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.929952448193773</v>
+        <v>0.4707463831214793</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.929952268304473</v>
+        <v>0.4707462032321791</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.929952309817389</v>
+        <v>0.4707462447450946</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.92995212300927</v>
+        <v>0.4707460579369753</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.929952192197462</v>
+        <v>0.4707461271251678</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.929951991551704</v>
+        <v>0.4707459264794099</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.92995203306462</v>
+        <v>0.4707459679923253</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.929952060739896</v>
+        <v>0.4707459956676022</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_5_000006.xlsx
+++ b/out/LSTM-S4_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.958776160273009</v>
+        <v>1.297446509901492</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002559727371013723</v>
+        <v>-0.0002259749444685876</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3294566415038532</v>
+        <v>0.2908473561320484</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.6595371953357327</v>
+        <v>0.5822451353676009</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07608517746417377</v>
+        <v>-0.06716860929674441</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2531154913025783</v>
+        <v>0.2234527718908354</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2531154913025783</v>
+        <v>0.2234527718908354</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2528466879493199</v>
+        <v>0.2232172755248575</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.8258220351288877</v>
+        <v>0.7234957669238816</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.90613516289671</v>
+        <v>1.671649458545733</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.158011741345247</v>
+        <v>0.1384327629011682</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.395131484814231</v>
+        <v>1.223963416942949</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2767723329611982</v>
+        <v>0.242478112920149</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.358776160273009</v>
+        <v>1.097446509901492</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.790742301011319</v>
+        <v>1.570554738557879</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1515708397016076</v>
+        <v>0.1327896002960584</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.358776160273009</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.816872650977054</v>
+        <v>1.593447301708709</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.06260096416645966</v>
+        <v>0.05484423558672241</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.481593977180774</v>
+        <v>0.4482190499120561</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.790344846120656</v>
+        <v>1.570206490668257</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.07799542929861515</v>
+        <v>0.06833121112586078</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.358776160273009</v>
+        <v>-0.2010084100773802</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.883745247842975</v>
+        <v>1.652033882692641</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04696273269945372</v>
+        <v>0.04114421560200386</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.2010084100773802</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.899623538460786</v>
+        <v>1.665944733267266</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03570519977904496</v>
+        <v>0.03127976656699432</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.924049955879539</v>
+        <v>1.687344266837198</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01579250278218995</v>
+        <v>0.01383455530691489</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.919898270341701</v>
+        <v>1.683706381994948</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01253039271187114</v>
+        <v>0.01097671023490683</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.929161942552878</v>
+        <v>1.691822195071252</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.006211178454313042</v>
+        <v>0.005440722533215087</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.929045999195319</v>
+        <v>1.691719981683243</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00360822732607189</v>
+        <v>0.00316311961199057</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.930050903165182</v>
+        <v>1.692600119269494</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001801613663035945</v>
+        <v>0.00157760520562247</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.930043653809215</v>
+        <v>1.69259314881918</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0008890155785007095</v>
+        <v>0.000776904300167823</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.930016022702859</v>
+        <v>1.692568321103126</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0005123361805749242</v>
+        <v>0.0004489207777947722</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.930154548917932</v>
+        <v>1.692689310605751</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001690936688898088</v>
+        <v>0.0001467739677500898</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.929976636127028</v>
+        <v>1.692532459110296</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>8.258585474357068e-05</v>
+        <v>7.135689900721546e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.929972605283798</v>
+        <v>1.692528317853836</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>4.147772647206162e-05</v>
+        <v>3.658533421184461e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.929975372216664</v>
+        <v>1.692530288335428</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.870180446963262e-05</v>
+        <v>1.633162402266935e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.929968820330935</v>
+        <v>1.692523891638271</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.92996919889918</v>
+        <v>1.692523734160768</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.929962531935309</v>
+        <v>1.692517067196897</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.929958669860213</v>
+        <v>1.692513205121801</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.929954122548028</v>
+        <v>1.692508657809616</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.929954212492678</v>
+        <v>1.692508747754266</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.929953354559093</v>
+        <v>1.69250788982068</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.929953582880128</v>
+        <v>1.692508118141715</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.929952787215916</v>
+        <v>1.692507322477504</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.929952849485289</v>
+        <v>1.692507384746877</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.929952877160566</v>
+        <v>1.692507412422154</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.929953029374589</v>
+        <v>1.692507564636176</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.929952683433627</v>
+        <v>1.692507218695215</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.929952759540639</v>
+        <v>1.692507294802227</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.9299529255923</v>
+        <v>1.692507460853888</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.9299532853709</v>
+        <v>1.692507820632488</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.929953306127358</v>
+        <v>1.692507841388946</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.929953409909646</v>
+        <v>1.692507945171234</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.929953638230681</v>
+        <v>1.692508173492269</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.929953513691935</v>
+        <v>1.692508048953523</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.929953541367212</v>
+        <v>1.6925080766288</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.929953596717766</v>
+        <v>1.692508131979354</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.929953859632897</v>
+        <v>1.692508394894484</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.929953776607066</v>
+        <v>1.692508311868654</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.929953569042489</v>
+        <v>1.692508104304077</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.929953582880128</v>
+        <v>1.692508118141715</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.929953721256512</v>
+        <v>1.6925082565181</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.929953437584924</v>
+        <v>1.692507972846511</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.929953264614443</v>
+        <v>1.692507799876031</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.929953160832155</v>
+        <v>1.692507696093742</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.929953306127358</v>
+        <v>1.692507841388946</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.929953548286031</v>
+        <v>1.692508083547619</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.929953375315551</v>
+        <v>1.692507910577138</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.929953077806324</v>
+        <v>1.692507613067912</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.929953063968685</v>
+        <v>1.692507599230273</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.929952697271266</v>
+        <v>1.692507232532853</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.929952697271266</v>
+        <v>1.692507232532853</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.929952635001893</v>
+        <v>1.69250717026348</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.929952531219604</v>
+        <v>1.692507066481192</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.929952358249123</v>
+        <v>1.692506893510711</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.929952406680858</v>
+        <v>1.692506941942445</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.929952046902258</v>
+        <v>1.692506582163846</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.929952005389343</v>
+        <v>1.69250654065093</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.929952060739896</v>
+        <v>1.692506596001484</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.92995211609045</v>
+        <v>1.692506651352038</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.929952157603366</v>
+        <v>1.692506692864953</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.929951887769416</v>
+        <v>1.692506423031003</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.929951943119969</v>
+        <v>1.692506478381557</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.929952088415173</v>
+        <v>1.692506623676761</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.929952053821077</v>
+        <v>1.692506589082665</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.929952039983439</v>
+        <v>1.692506575245027</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.929952129928089</v>
+        <v>1.692506665189677</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.929952448193773</v>
+        <v>1.692506983455361</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.929952268304473</v>
+        <v>1.692506803566061</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.929952309817389</v>
+        <v>1.692506845078976</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.92995212300927</v>
+        <v>1.692506658270857</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.929952192197462</v>
+        <v>1.692506727459049</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.929951991551704</v>
+        <v>1.692506526813292</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.92995203306462</v>
+        <v>1.692506568326207</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.481593977180774</v>
+        <v>-0.8502358700668163</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.929952060739896</v>
+        <v>1.692506596001484</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_5_000006.xlsx
+++ b/out/LSTM-S4_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.00393686443567276</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.002379603683948517</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.00210145115852356</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.002176929265260696</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.297446509901492</v>
+        <v>-0.3</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.002076976001262665</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.297446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.002213921397924423</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.297446509901492</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.002428721636533737</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.297446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.002890385687351227</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.297446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.003082830458879471</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.297446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.003080431371927261</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.097446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.003005210310220718</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.097446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002969123423099518</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.097446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.003081310540437698</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.002927236258983612</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.002911482006311417</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.00291559100151062</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.003169260919094086</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.097446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.003391440957784653</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.097446509901492</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.003610983490943909</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.097446509901492</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.003560986369848251</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.097446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.003331035375595093</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.003095962107181549</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.003046128898859024</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.003267969936132431</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.16</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.0032343789935112</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.00345265120267868</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.097446509901492</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.003997690975666046</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.097446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003932587802410126</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.097446509901492</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.003520332276821136</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.097446509901492</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.003172852098941803</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.097446509901492</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002832751721143723</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.002441778779029846</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.002312235534191132</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.002639215439558029</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.002627942711114883</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.002624694257974625</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.002695724368095398</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.002502128481864929</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.002441156655550003</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.002327475696802139</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.002341505140066147</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.002549104392528534</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.003032207489013672</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0002259749444685876</v>
+        <v>-8.622523744986393e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2908473561320484</v>
+        <v>0.1109783867584393</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.002915911376476288</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.5822451353676009</v>
+        <v>0.2221672198927833</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.06716860929674441</v>
+        <v>-0.02562956828144246</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.001838870346546173</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.2234527718908354</v>
+        <v>0.08526259323954699</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.001387201249599457</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.2234527718908354</v>
+        <v>0.08526259323954699</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.001199960708618164</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.2232172755248575</v>
+        <v>0.08524552522815508</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.7234957669238816</v>
+        <v>0.05243662228332394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.0006719045341014862</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.671649458545733</v>
+        <v>0.1902231833656721</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1384327629011682</v>
+        <v>0.0100330947394741</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.0005842149257659912</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.223963416942949</v>
+        <v>0.1577763539392142</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.242478112920149</v>
+        <v>0.01757391695572542</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.0002930313348770142</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.097446509901492</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.570554738557879</v>
+        <v>0.1828963226039414</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1327896002960584</v>
+        <v>0.009622887379975747</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>1.574307680130005e-05</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.593447301708709</v>
+        <v>0.1845540646375362</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.05484423558672241</v>
+        <v>0.003971316575017368</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.000415310263633728</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.4482190499120561</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.570206490668257</v>
+        <v>0.1828661330212101</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.06833121112586078</v>
+        <v>0.004948910165420396</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>4.32133674621582e-07</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.2010084100773802</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.652033882692641</v>
+        <v>0.1887937585988229</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.04114421560200386</v>
+        <v>0.002978468247674992</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0005954839289188385</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.2010084100773802</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.665944733267266</v>
+        <v>0.1897981147489429</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.03127976656699432</v>
+        <v>0.00226231874709202</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0004883371293544769</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.687344266837198</v>
+        <v>0.1913450621814756</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01383455530691489</v>
+        <v>0.0009978432933696935</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.002052389085292816</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.683706381994948</v>
+        <v>0.191076623178886</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.01097671023490683</v>
+        <v>0.0007920189329881852</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.003396451473236084</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.691822195071252</v>
+        <v>0.1916609391585102</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.005440722533215087</v>
+        <v>0.0003902338816021974</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.002317745238542557</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.691719981683243</v>
+        <v>0.1916488852146496</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.00316311961199057</v>
+        <v>0.0002248268589047337</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002186466008424759</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.692600119269494</v>
+        <v>0.1917080962975824</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.00157760520562247</v>
+        <v>0.0001084588290795521</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.003838337957859039</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.69259314881918</v>
+        <v>0.1917029550336809</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000776904300167823</v>
+        <v>5.249296324763405e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.00512642040848732</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.692568321103126</v>
+        <v>0.1916964996570665</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004489207777947722</v>
+        <v>2.837652777902737e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.005987856537103653</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.692689310605751</v>
+        <v>0.1917007295057236</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001467739677500898</v>
+        <v>6.159850569859539e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.007087633013725281</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.692532459110296</v>
+        <v>0.1916846453524607</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>7.135689900721546e-05</v>
+        <v>-5.08417705457914e-07</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.007782183587551117</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.692528317853836</v>
+        <v>0.1916797088904462</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.658533421184461e-05</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.008351981639862061</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.692530288335428</v>
+        <v>0.1916753077618412</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.633162402266935e-05</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.008377909660339355</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.692523891638271</v>
+        <v>0.1916701525732684</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.008245162665843964</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.692523734160768</v>
+        <v>0.1916706922411686</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.008411087095737457</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.692517067196897</v>
+        <v>0.1916703601378454</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.008415982127189636</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.692513205121801</v>
+        <v>0.1916707406729031</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.008842699229717255</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.692508657809616</v>
+        <v>0.1916709689939378</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.009464055299758911</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.692508747754266</v>
+        <v>0.1916710589385878</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.01004352420568466</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.69250788982068</v>
+        <v>0.191670201005003</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.01042414084076881</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.692508118141715</v>
+        <v>0.1916704293260376</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.01029563695192337</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.692507322477504</v>
+        <v>0.1916696336618259</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01035184785723686</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.692507384746877</v>
+        <v>0.191669695931199</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.01030958071351051</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.692507412422154</v>
+        <v>0.1916697236064759</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.0100335069000721</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.692507564636176</v>
+        <v>0.1916698758204992</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.009934965521097183</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.692507218695215</v>
+        <v>0.1916695298795374</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.009560283273458481</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.692507294802227</v>
+        <v>0.1916696059865491</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.009526904672384262</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.692507460853888</v>
+        <v>0.1916697720382106</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.008993323892354965</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.692507820632488</v>
+        <v>0.1916701318168107</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.008586987853050232</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.692507841388946</v>
+        <v>0.1916701525732684</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.008433546870946884</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.692507945171234</v>
+        <v>0.1916702563555569</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.008924327790737152</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.692508173492269</v>
+        <v>0.1916704846765916</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.009719561785459518</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.692508048953523</v>
+        <v>0.1916703601378454</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.01028882339596748</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.6925080766288</v>
+        <v>0.1916703878131222</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.01013258099555969</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.692508131979354</v>
+        <v>0.1916704431636762</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01051858440041542</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.692508394894484</v>
+        <v>0.1916707060788069</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.01066157966852188</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.692508311868654</v>
+        <v>0.1916706230529761</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.01066385209560394</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.692508104304077</v>
+        <v>0.1916704154883993</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.01057156175374985</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.692508118141715</v>
+        <v>0.1916704293260376</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.01049549877643585</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.6925082565181</v>
+        <v>0.1916705677024224</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01050005480647087</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.692507972846511</v>
+        <v>0.1916702840308337</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01067890599370003</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.692507799876031</v>
+        <v>0.191670111060353</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.0103401318192482</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.692507696093742</v>
+        <v>0.1916700072780645</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.01024153828620911</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.692507841388946</v>
+        <v>0.1916701525732684</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01016615703701973</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.692508083547619</v>
+        <v>0.1916703947319416</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01009490340948105</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.692507910577138</v>
+        <v>0.1916702217614606</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.01012910157442093</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.16</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.692507613067912</v>
+        <v>0.1916699242522337</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.0100753977894783</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.692507599230273</v>
+        <v>0.1916699104145952</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.009982652962207794</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.692507232532853</v>
+        <v>0.191669543717176</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.009692039340734482</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.692507232532853</v>
+        <v>0.191669543717176</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.00941154733300209</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.69250717026348</v>
+        <v>0.1916694814478029</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.009321775287389755</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.692507066481192</v>
+        <v>0.1916693776655144</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.009205788373947144</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.692506893510711</v>
+        <v>0.1916692046950336</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.008810073137283325</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.692506941942445</v>
+        <v>0.1916692531267682</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.008384127169847488</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.692506582163846</v>
+        <v>0.1916688933481681</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.007910609245300293</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.69250654065093</v>
+        <v>0.1916688518352527</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.007313605397939682</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.692506596001484</v>
+        <v>0.1916689071858064</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.007112696766853333</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.692506651352038</v>
+        <v>0.1916689625363604</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.006926532834768295</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.692506692864953</v>
+        <v>0.1916690040492758</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.006655681878328323</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.692506423031003</v>
+        <v>0.1916687342153257</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.006248787045478821</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.692506478381557</v>
+        <v>0.1916687895658796</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.005947418510913849</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.692506623676761</v>
+        <v>0.1916689348610835</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.005637217313051224</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.692506589082665</v>
+        <v>0.1916689002669873</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005463089793920517</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.692506575245027</v>
+        <v>0.1916688864293487</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.004966113716363907</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.692506665189677</v>
+        <v>0.1916689763739989</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.004214026033878326</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.692506983455361</v>
+        <v>0.1916692946396836</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.004551488906145096</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.692506803566061</v>
+        <v>0.1916691147503834</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.005032993853092194</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.692506845078976</v>
+        <v>0.1916691562632988</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.005203809589147568</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.8502358700668163</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.692506658270857</v>
+        <v>0.1916689694551795</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.005340352654457092</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.692506727459049</v>
+        <v>0.191669038643372</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.00534839928150177</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.692506526813292</v>
+        <v>0.1916688379976142</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.005353789776563644</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.3000000000000002</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.692506568326207</v>
+        <v>0.1916688795105296</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00523405522108078</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.8502358700668163</v>
+        <v>-0.4400000000000002</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.692506596001484</v>
+        <v>0.1916689071858064</v>
       </c>
     </row>
   </sheetData>
